--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Incursion_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Incursion_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd8e0fb93542648e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Ra5a57e0094cc43f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb4d3572e59254e40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R787ab6d71f0e4de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R0ad6f218cf1d4ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rbd4af0ad25984296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R517856548f0b44ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R4c7bef0ef8e14fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R2ee945f054c3493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R32b90d933a854cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R3611b3113efd4809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R9836f5065c724cb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R2ef1405691954396"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R782feeb84baa45aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R6038f58b1b4e4a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rdcb09173034b4eaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R62de488a9ab04917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R6e76e3ff46484008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rdf143531fac44952"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rb8a9d6fbf16d4999"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R31b6e314d7584710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R39f6fdc6be6c4612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R1875c8a650c440f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R539983fea95b46cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R67e1fae5d664463e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R7bd415cb72f0401d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Ree9f71fd2cd94080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R78496aff5b7b4bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0d2a60a9eca84528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R0039209fadd64901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Ra5060978fffc4453"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf0a971b51f5e4683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rb300b1d0a3f246ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R847204a18fa540eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R1510705376f24bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rdb55e5f8a9d142ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdf07fa6607be4e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R719c781ffa3941f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7a494acce71d4b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rb8a64ed8778a4284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R3bdf87f624ee46f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2422a44fa34c4a67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R2ed28a84c4c64bf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R0d92d950451441ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R3138808567084d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf449c5416ec04be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rcff5deee17164b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R79fe88a556ab4411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R7c640361700741c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R2b76dd6e39894657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re1b47f1b89604a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rd1040b2a65454845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R82e6f348bb594d29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R864e27eedc8e4d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9bbe4e657ab14840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Ra60fe09b3b154059"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -222,9 +222,6 @@
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -266,9 +263,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>64</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>8</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>52</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="26" t="str">
+      <x:c r="A9" s="25" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="27" t="str">
+      <x:c r="B9" s="26" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="27" t="str">
+      <x:c r="C9" s="26" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="27" t="str">
+      <x:c r="D9" s="26" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="27" t="str">
+      <x:c r="E9" s="26" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="27" t="str">
+      <x:c r="F9" s="26" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="27" t="str">
+      <x:c r="G9" s="26" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="27" t="str">
+      <x:c r="H9" s="26" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="27" t="str">
+      <x:c r="I9" s="26" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="27" t="str">
+      <x:c r="J9" s="26" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="27" t="str">
+      <x:c r="K9" s="26" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="27" t="str">
+      <x:c r="L9" s="26" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="28" t="str">
+      <x:c r="M9" s="27" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Défini")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$12,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
-        <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$9,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$12,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="19" t="str">
+      <x:c r="A37" s="18" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>52</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4048,15 +4042,15 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="17" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S7" s="17" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-EN-COLLECTOR</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -4065,10 +4059,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -4105,10 +4099,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INC-S-PAIR</x:v>
       </x:c>
-      <x:c r="R8" s="32" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S8" s="32" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4162,10 +4156,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="17" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S9" s="17" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4201,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb41f5d6d8ae241be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b165dbe337a49cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4341,61 +4335,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4449,11 +4443,11 @@
         <x:v>Conception originale rattachée à Mass Effect: Incursion, récit court</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-MAIN</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -4462,10 +4456,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -4502,8 +4496,8 @@
         <x:v>Conception originale rattachée à Mass Effect: Incursion, récit court</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -4555,8 +4549,8 @@
         <x:v>Conception originale rattachée à Mass Effect: Incursion, récit court</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -4590,7 +4584,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcca84afc1ce4f39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73b9aa6c5fa40ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4730,61 +4724,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4838,11 +4832,11 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-SIDE</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -4851,10 +4845,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P2</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -4891,8 +4885,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -4944,8 +4938,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -4979,7 +4973,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0e8c59c1530437c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eaa8c25e08f4f21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5119,61 +5113,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5227,11 +5221,11 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-CHOICE</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -5240,10 +5234,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -5280,8 +5274,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -5333,8 +5327,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5368,7 +5362,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a18d1ed051b4473"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf454afd6d8c841d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5508,61 +5502,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5616,11 +5610,11 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-DIA</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -5629,10 +5623,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -5669,8 +5663,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -5722,8 +5716,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5757,7 +5751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbde62d1654074fff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad92d715a0ec4ef6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5897,61 +5891,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6003,11 +5997,11 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-CINE</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -6016,10 +6010,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -6054,8 +6048,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -6105,8 +6099,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -6140,7 +6134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4df1f16f32d4ea5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e19779b3120424b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6280,61 +6274,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6386,8 +6380,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -6421,7 +6415,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30bc47a819d3468f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7d5c11b562c419b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6561,61 +6555,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6667,8 +6661,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -6702,7 +6696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2394dbe70589433d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red05bdb25d624fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6842,61 +6836,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6948,8 +6942,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -6983,7 +6977,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f83bcf881a447bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79809df81954a35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7123,61 +7117,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7231,11 +7225,11 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-ALLY-GUARDS</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -7244,10 +7238,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -7284,8 +7278,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -7319,7 +7313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5541069492734b77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb10617890618479a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7459,61 +7453,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7567,10 +7561,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INC-S-PAIR</x:v>
       </x:c>
-      <x:c r="R7" s="17" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S7" s="17" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -7606,7 +7600,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57d77c3a051f434f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a78cff80711418b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7746,61 +7740,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7854,11 +7848,11 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-EN-SUNS-M2</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -7867,10 +7861,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -7907,8 +7901,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -7960,11 +7954,11 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="31" t="str">
+      <x:c r="A10" s="30" t="str">
         <x:v>INC-EN-COLLECTOR-M2</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
@@ -7973,10 +7967,10 @@
       <x:c r="C10" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="str">
+      <x:c r="D10" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="str">
+      <x:c r="E10" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
@@ -8013,8 +8007,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="32" t="str"/>
-      <x:c r="S10" s="32" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="16" t="str">
@@ -8066,11 +8060,11 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="17" t="str"/>
-      <x:c r="S11" s="17" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="31" t="str">
+      <x:c r="A12" s="30" t="str">
         <x:v>INC-EN-PRAETORIAN-M2</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
@@ -8079,10 +8073,10 @@
       <x:c r="C12" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="str">
+      <x:c r="D12" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="str">
+      <x:c r="E12" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
@@ -8119,8 +8113,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="32" t="str"/>
-      <x:c r="S12" s="32" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -8154,7 +8148,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11e7cc7cf62646d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf94280222dda4543"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8294,61 +8288,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8400,11 +8394,11 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-ANI-GUARDS</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -8413,10 +8407,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -8451,8 +8445,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8486,7 +8480,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f07ffdf48414a76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25881ee55beb464d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8626,61 +8620,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8730,11 +8724,11 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SPR-GUARDS</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -8743,10 +8737,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -8779,8 +8773,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8814,7 +8808,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R647f72471b184644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b3d5ee6ff414d9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8954,61 +8948,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9060,11 +9054,11 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-VFX</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -9073,10 +9067,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -9111,8 +9105,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -9162,8 +9156,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -9197,7 +9191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racfaa13e80f14795"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40525e1cf94844e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9337,61 +9331,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9445,8 +9439,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -9480,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd57a023e6824cfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7bd66a3a85d4b5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9620,61 +9614,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9722,11 +9716,11 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SYS-GROUP</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -9735,10 +9729,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -9769,8 +9763,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -9816,11 +9810,11 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="31" t="str">
+      <x:c r="A10" s="30" t="str">
         <x:v>INC-SYS-SAVE</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
@@ -9829,10 +9823,10 @@
       <x:c r="C10" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="str">
+      <x:c r="D10" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="str">
+      <x:c r="E10" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
@@ -9863,8 +9857,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="32" t="str"/>
-      <x:c r="S10" s="32" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9898,7 +9892,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79256bf94b5c4d24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84df9523451f466b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10038,61 +10032,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10140,11 +10134,11 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-QA</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -10153,10 +10147,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -10187,8 +10181,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -10234,11 +10228,11 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="31" t="str">
+      <x:c r="A10" s="30" t="str">
         <x:v>INC-QA-SOURCE</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
@@ -10247,10 +10241,10 @@
       <x:c r="C10" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="str">
+      <x:c r="D10" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="str">
+      <x:c r="E10" s="29" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
@@ -10279,8 +10273,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="32" t="str"/>
-      <x:c r="S10" s="32" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="16" t="str">
@@ -10324,11 +10318,11 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="17" t="str"/>
-      <x:c r="S11" s="17" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
-      <x:c r="A12" s="31" t="str">
+      <x:c r="A12" s="30" t="str">
         <x:v>INC-QA-NARRATIVE</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
@@ -10337,10 +10331,10 @@
       <x:c r="C12" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="str">
+      <x:c r="D12" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="str">
+      <x:c r="E12" s="29" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
@@ -10369,8 +10363,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="32" t="str"/>
-      <x:c r="S12" s="32" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -10404,7 +10398,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97b2f511ce614a44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R091d706251294c2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10544,61 +10538,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10644,11 +10638,11 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-CNT-NO-CUT</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -10657,10 +10651,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -10689,8 +10683,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -10724,7 +10718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61fe610a141348c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d3109bf6d84de7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10789,10 +10783,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
+      <x:c r="B6" s="27" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -10841,7 +10835,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Enquête brève, confrontation concentrée et lecture d’un indice. Le système de jeu proposé ne transforme pas le récit en campagne de libération de colonies.</x:v>
+        <x:v>64 fiches de production ; 2 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -10860,11 +10854,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -11017,22 +11011,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="26" t="str">
+      <x:c r="A26" s="25" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="27" t="str">
+      <x:c r="B26" s="26" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="str">
+      <x:c r="C26" s="26" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="27" t="str">
+      <x:c r="D26" s="26" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="27" t="str">
+      <x:c r="E26" s="26" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="28" t="str">
+      <x:c r="F26" s="27" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -11121,13 +11115,13 @@
       <x:c r="F32" s="2"/>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="26" t="str">
+      <x:c r="A33" s="25" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B33" s="27" t="str">
+      <x:c r="B33" s="26" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C33" s="28" t="str">
+      <x:c r="C33" s="27" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D33" s="2"/>
@@ -11498,10 +11492,16 @@
       <x:c r="E59" s="2"/>
       <x:c r="F59" s="2"/>
     </x:row>
-    <x:row r="60" ht="22" customHeight="1">
-      <x:c r="A60" s="2"/>
-      <x:c r="B60" s="2"/>
-      <x:c r="C60" s="2"/>
+    <x:row r="60" ht="96" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
+        <x:v>2 références supplémentaires au stade Prototype dans 1 parcours de lecture (1 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D60" s="2"/>
       <x:c r="E60" s="2"/>
       <x:c r="F60" s="2"/>
@@ -12057,6 +12057,14 @@
       <x:c r="D129" s="2"/>
       <x:c r="E129" s="2"/>
       <x:c r="F129" s="2"/>
+    </x:row>
+    <x:row r="130" ht="22" customHeight="1">
+      <x:c r="A130" s="2"/>
+      <x:c r="B130" s="2"/>
+      <x:c r="C130" s="2"/>
+      <x:c r="D130" s="2"/>
+      <x:c r="E130" s="2"/>
+      <x:c r="F130" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12198,61 +12206,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12306,10 +12314,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="17" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S7" s="17" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -12345,7 +12353,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ca07f60402d42e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfba4390cc9f346d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12372,7 +12380,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="71" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -12485,65 +12493,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="16" t="str">
         <x:v>INC-REF-SCOPE</x:v>
       </x:c>
@@ -12551,7 +12559,7 @@
         <x:v>Aria et les Collectors</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
         <x:v>Établi</x:v>
@@ -12570,7 +12578,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification INC/lore/ref-scope; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire INC-REF-SCOPE consultable dans les lectures inc-omega de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Vérifier toute précision non contenue dans cette notice avant de la déclarer canon.</x:v>
@@ -12585,15 +12593,15 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INC-S-PAIR</x:v>
       </x:c>
-      <x:c r="R7" s="17" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S7" s="17" t="str">
-        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-REF-TIMING</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -12602,10 +12610,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -12634,10 +12642,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="32" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S8" s="32" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -12683,15 +12691,15 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R9" s="17" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S9" s="17" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="31" t="str">
+      <x:c r="A10" s="30" t="str">
         <x:v>INC-SC-CHECK-REF</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
@@ -12700,10 +12708,10 @@
       <x:c r="C10" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="str">
+      <x:c r="D10" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="str">
+      <x:c r="E10" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
@@ -12732,10 +12740,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R10" s="32" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S10" s="32" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -12781,15 +12789,15 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R11" s="17" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S11" s="17" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="31" t="str">
+      <x:c r="A12" s="30" t="str">
         <x:v>INC-SC-REPORT-REF</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
@@ -12798,10 +12806,10 @@
       <x:c r="C12" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="str">
+      <x:c r="D12" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="str">
+      <x:c r="E12" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
@@ -12830,10 +12838,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INC-S-WIKI</x:v>
       </x:c>
-      <x:c r="R12" s="32" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect%3A_Incursion</x:v>
       </x:c>
-      <x:c r="S12" s="32" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -12869,7 +12877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree1d5517b43b424b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a83faf098b4615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12896,7 +12904,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="71" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="90" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -13009,65 +13017,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="16" t="str">
         <x:v>INC-WRL-OMEGA</x:v>
       </x:c>
@@ -13075,7 +13083,7 @@
         <x:v>Omega — secteur du raid</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
         <x:v>Établi</x:v>
@@ -13096,7 +13104,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Livrable proposé : spécification INC/worlds/wrl-omega; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire INC-WRL-OMEGA consultable dans les lectures inc-omega de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Le résultat narratif du raid reste fixé; une tâche de gameplay ne réécrit pas le sort des captifs ni ne fait d’Aria la libératrice de toutes les colonies.</x:v>
@@ -13111,11 +13119,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INC-S-PAIR</x:v>
       </x:c>
-      <x:c r="R7" s="17" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://books.apple.com/gr/book/mass-effect-incursion-inquisition/id1047054838</x:v>
       </x:c>
-      <x:c r="S7" s="17" t="str">
-        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13150,7 +13158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R287c36b0850a4564"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda529d378ef5461c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13290,61 +13298,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13396,8 +13404,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -13431,7 +13439,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4640e78174af425f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3953d15f3464097"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13571,61 +13579,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13675,8 +13683,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -13710,7 +13718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5138e72ff9d74be9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cd31e8bb40c4cee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13850,61 +13858,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13954,8 +13962,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -13989,7 +13997,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cb9108d437246a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92947b8de3174022"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14129,61 +14137,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="27" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="27" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="27" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="27" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="27" t="str">
+      <x:c r="G6" s="26" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="27" t="str">
+      <x:c r="H6" s="26" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="27" t="str">
+      <x:c r="I6" s="26" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="27" t="str">
+      <x:c r="J6" s="26" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="27" t="str">
+      <x:c r="K6" s="26" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="27" t="str">
+      <x:c r="L6" s="26" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="27" t="str">
+      <x:c r="M6" s="26" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="27" t="str">
+      <x:c r="N6" s="26" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="27" t="str">
+      <x:c r="O6" s="26" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="27" t="str">
+      <x:c r="P6" s="26" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="27" t="str">
+      <x:c r="Q6" s="26" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="27" t="str">
+      <x:c r="R6" s="26" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="28" t="str">
+      <x:c r="S6" s="27" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14237,11 +14245,11 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="17" t="str"/>
-      <x:c r="S7" s="17" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="30" t="str">
         <x:v>INC-SC-RAID-PROP</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -14250,10 +14258,10 @@
       <x:c r="C8" s="14" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="str">
+      <x:c r="D8" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
@@ -14290,8 +14298,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="32" t="str"/>
-      <x:c r="S8" s="32" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -14343,8 +14351,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="17" t="str"/>
-      <x:c r="S9" s="17" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -14378,7 +14386,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf32046d4d0a47ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8498ff342ba840dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Incursion_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Incursion_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0d2a60a9eca84528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R0039209fadd64901"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Ra5060978fffc4453"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf0a971b51f5e4683"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rb300b1d0a3f246ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R847204a18fa540eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R1510705376f24bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rdb55e5f8a9d142ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdf07fa6607be4e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R719c781ffa3941f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7a494acce71d4b85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rb8a64ed8778a4284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R3bdf87f624ee46f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2422a44fa34c4a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R2ed28a84c4c64bf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R0d92d950451441ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R3138808567084d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf449c5416ec04be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rcff5deee17164b32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R79fe88a556ab4411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R7c640361700741c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R2b76dd6e39894657"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re1b47f1b89604a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rd1040b2a65454845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R82e6f348bb594d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R864e27eedc8e4d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R9bbe4e657ab14840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Ra60fe09b3b154059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbe8565ef9a5f438b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc51b47c950054d9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R7e80e8085d46458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R9cb88bbafe7e4082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re1376f7f699740e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rb83f858ca8964364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rd5104163873b4759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rbabee2c7aaa44923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R139d5655d56241c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rb3442ffe1d014f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R4a634aebe1c647fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R66d73b6520234eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4fc48b669d644205"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R7c056081f5ed47b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3543fcfa6ce54110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rfb40a46a992d47e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R56d659a5ae964971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdf7c737d49ad4c99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R4a4585b87794402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R447c32a1d6d548ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rd4c7a3d1dd3e4936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R3a97a71b89374d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc9612e2490d0431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R52e166215e3c4a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rf18eb03078284f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf311d7c21a764bb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rd331db1a8514453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R931d1b29bd744dff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b165dbe337a49cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb91657603e40fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4584,7 +4584,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb73b9aa6c5fa40ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8ed48bc5e64e73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4973,7 +4973,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eaa8c25e08f4f21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdb48f2fcf314c2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5362,7 +5362,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf454afd6d8c841d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R802ef5b6a5f94364"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5751,7 +5751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad92d715a0ec4ef6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4162d1db07b4497c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6134,7 +6134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e19779b3120424b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779778f01976458f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6415,7 +6415,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7d5c11b562c419b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151410f902df4ddb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6696,7 +6696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red05bdb25d624fba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cc2f2fa5fdc477f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6977,7 +6977,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79809df81954a35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd64fb6b1c8a4ec5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7313,7 +7313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb10617890618479a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48d7a4123e4d411c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7600,7 +7600,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a78cff80711418b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red112e581dca45b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8148,7 +8148,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf94280222dda4543"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3068c053afe644ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8480,7 +8480,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25881ee55beb464d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67359396b3d4e3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8808,7 +8808,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b3d5ee6ff414d9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R817c62172db147f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9191,7 +9191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40525e1cf94844e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346b3cc7028e47d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7bd66a3a85d4b5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra85554644f4446c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9892,7 +9892,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84df9523451f466b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd695f1449d5444f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10398,7 +10398,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R091d706251294c2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ded88fc49f84860"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10718,7 +10718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d3109bf6d84de7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2e15d8d2c1848b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12353,7 +12353,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfba4390cc9f346d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b71b2d20fe464a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12877,7 +12877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a83faf098b4615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d028129b028412e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13158,7 +13158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda529d378ef5461c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea84c92844749d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13439,7 +13439,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3953d15f3464097"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e9303eb1d3e4adb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13718,7 +13718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cd31e8bb40c4cee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ce6df6c8cc46a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13997,7 +13997,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92947b8de3174022"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12a7081453db4849"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14386,7 +14386,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8498ff342ba840dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0422fb95e34d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Incursion_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Incursion_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbe8565ef9a5f438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc51b47c950054d9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R7e80e8085d46458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R9cb88bbafe7e4082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re1376f7f699740e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rb83f858ca8964364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rd5104163873b4759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rbabee2c7aaa44923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R139d5655d56241c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rb3442ffe1d014f39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R4a634aebe1c647fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R66d73b6520234eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4fc48b669d644205"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R7c056081f5ed47b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3543fcfa6ce54110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rfb40a46a992d47e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R56d659a5ae964971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdf7c737d49ad4c99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R4a4585b87794402f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R447c32a1d6d548ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rd4c7a3d1dd3e4936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R3a97a71b89374d93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc9612e2490d0431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R52e166215e3c4a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rf18eb03078284f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf311d7c21a764bb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rd331db1a8514453f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R931d1b29bd744dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R11cdad2292b64659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R33a49bf9e2e74a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R03b83250203545ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R2eed80ba22454e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R81e6448c8ed04460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R4b4e5f23be1e4c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R31b542ba076746ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R1584b2b4c5f74115"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R487ed36fb6a44689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Re3626502a5fc485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R9ed229fb30854235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rc647aba187ed490f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5c590cf5ab9442f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R75fb34ea7a4b4902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rbb3f19d1efcc4ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rf8f498fb8077424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R2e768a6b7ade4cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R29485e54ce444b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R5d9d59684fcb4067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R794cee9cdccc4189"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R3f4ce540f2a04895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R52d815328c4b41ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R74d8be56a4554317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5b3f37e8c5a34566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Ref7c370bb66e4bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R6bd6e82756434d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rc96ffc49468345e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rd2ee17b0bf404f82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb91657603e40fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9cc5f7bcf5a4447"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4584,7 +4584,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8ed48bc5e64e73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eedd667b6da4094"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4973,7 +4973,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdb48f2fcf314c2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79b51c409c874dc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5362,7 +5362,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R802ef5b6a5f94364"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9663c8cd5e7f4ba7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5751,7 +5751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4162d1db07b4497c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17c795e279cc4050"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6134,7 +6134,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R779778f01976458f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01d9e5ffd32b456e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6415,7 +6415,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R151410f902df4ddb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9fb130934f4592"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6696,7 +6696,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cc2f2fa5fdc477f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9863b1c58f3a4dcd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6977,7 +6977,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd64fb6b1c8a4ec5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0893db1b4b2a4523"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7313,7 +7313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48d7a4123e4d411c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a6f9b13b3f745bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7600,7 +7600,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red112e581dca45b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfada65a86a714b65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8148,7 +8148,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3068c053afe644ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad1feb48d5e04831"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8480,7 +8480,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67359396b3d4e3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce626a5b45a14983"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8808,7 +8808,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R817c62172db147f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a4be9b538104213"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9191,7 +9191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346b3cc7028e47d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d57963f31fb4c57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra85554644f4446c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1604635d0118442a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9892,7 +9892,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd695f1449d5444f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41653a2e1b21475e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10398,7 +10398,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ded88fc49f84860"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77cb9b7466f64c51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10718,7 +10718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2e15d8d2c1848b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41bcd67d45d64e34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12353,7 +12353,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59b71b2d20fe464a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7418ba34aef64aa7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12877,7 +12877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d028129b028412e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d82076f030f426e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13158,7 +13158,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea84c92844749d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R707387b45115497d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13439,7 +13439,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e9303eb1d3e4adb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb03e0cd3e01d4409"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13718,7 +13718,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ce6df6c8cc46a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfe81f5413ae4cfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13997,7 +13997,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12a7081453db4849"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b0740b71aa04368"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14386,7 +14386,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0422fb95e34d29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R331055f4b8a7477f"/>
   </x:tableParts>
 </x:worksheet>
 </file>